--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260729.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260729.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>43,964,027</t>
+          <t>44,002,027</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>66.89%</t>
+          <t>67.32%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2,654,703</t>
+          <t>2,656,703</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>5.87%</t>
+          <t>5.82%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>22,020,000</t>
+          <t>22,039,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.63%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>5,983,267</t>
+          <t>5,988,267</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>21,035,286</t>
+          <t>21,053,286</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>524,000</t>
+          <t>525,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
@@ -743,51 +743,51 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2,378,901</t>
+          <t>2,380,901</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2,839,608</t>
+          <t>4,770,285</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>4,766,285</t>
+          <t>2,842,608</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>5,445,520</t>
+          <t>5,450,520</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>1,217,617</t>
+          <t>1,218,617</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
@@ -902,51 +902,51 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>5,579,296</t>
+          <t>2,059,288</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>2,057,288</t>
+          <t>5,583,296</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -968,51 +968,51 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>3,527,000</t>
+          <t>169,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>169,000</t>
+          <t>3,530,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1051,188 +1051,188 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>13,237,134</t>
+          <t>13,248,134</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>103,000</t>
+          <t>1,376,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>1,375,000</t>
+          <t>103,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>144,482</t>
+          <t>157,499</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>157,499</t>
+          <t>1,030,822</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,029,822</t>
+          <t>144,482</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.33%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>619,600</t>
+          <t>831,897</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>2,058,587</t>
+          <t>620,600</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>831,897</t>
+          <t>2,060,587</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
@@ -1254,29 +1254,29 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>594,000</t>
+          <t>387,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
@@ -1293,73 +1293,73 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>3,312,000</t>
+          <t>3,315,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>386,000</t>
+          <t>594,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,884,000</t>
+          <t>963,659</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>5,881,000</t>
+          <t>1,885,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,230,441</t>
+          <t>5,886,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,22 +1393,22 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>962,659</t>
+          <t>2,671,703</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,577,981</t>
+          <t>3,580,981</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>2,669,703</t>
+          <t>1,231,441</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1481,39 +1481,39 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>1,417,384</t>
+          <t>4,582,578</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>149,386</t>
+          <t>10,906,121</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>46,000</t>
+          <t>7,375,249</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>4,578,578</t>
+          <t>1,418,384</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,39 +1569,39 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>10,897,121</t>
+          <t>150,386</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>7,369,249</t>
+          <t>46,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>598,000</t>
+          <t>599,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2,251,107</t>
+          <t>2,253,107</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>1,218,076</t>
+          <t>1,219,076</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>5,098,956</t>
+          <t>5,102,956</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>827,000</t>
+          <t>1,605,400</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>298,000</t>
+          <t>299,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,66 +1789,66 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>1,603,400</t>
+          <t>828,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>187,000</t>
+          <t>96,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>96,000</t>
+          <t>187,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>234,000</t>
+          <t>512,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>511,000</t>
+          <t>234,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>328,000</t>
+          <t>1,808,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,031,121</t>
+          <t>1,032,121</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,807,000</t>
+          <t>67,538</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>67,538</t>
+          <t>401,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,39 +2009,39 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>401,000</t>
+          <t>329,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>175,000</t>
+          <t>341,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,22 +2053,22 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>340,000</t>
+          <t>183,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>183,000</t>
+          <t>261,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>261,000</t>
+          <t>175,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>118,000</t>
+          <t>74,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>74,000</t>
+          <t>345,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -2207,17 +2207,17 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>345,000</t>
+          <t>118,000</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>1,710,767,076</t>
+          <t>1,566,651,583</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>262,831,346</t>
+          <t>228,233,346</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>-1,298,571,984</t>
+          <t>-1,308,178,905</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr"/>
